--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/.julia/dev/JPEtools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/damandhaliwal/Documents/Research Work/JPE/Replications/JPE-Sprenger-20250266/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957E4354-791A-4942-ABF7-9C88724FEAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85CCBE0-16FC-8246-9F2B-84C66B6F4020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30080" yWindow="600" windowWidth="30080" windowHeight="32520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="103">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -45,7 +45,295 @@
     <t>Line Number</t>
   </si>
   <si>
-    <t>In-text numbers</t>
+    <t>cleaned-data/ExperimentData.dta and .csv</t>
+  </si>
+  <si>
+    <t>cleaned-data/demographics.dta and .csv</t>
+  </si>
+  <si>
+    <t>cleaned-data/part1_cleaned.dta and .csv</t>
+  </si>
+  <si>
+    <t>cleaned-data/part2_cleaned.dta and .csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cleaned-data/[dataset]_definitions.csv </t>
+  </si>
+  <si>
+    <t>clean_data.do</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Figure 1</t>
+  </si>
+  <si>
+    <t>Figure 3</t>
+  </si>
+  <si>
+    <t>Figure 4</t>
+  </si>
+  <si>
+    <t>Figure 5</t>
+  </si>
+  <si>
+    <t>Figure 6</t>
+  </si>
+  <si>
+    <t>Figure 7</t>
+  </si>
+  <si>
+    <t>Figure 8</t>
+  </si>
+  <si>
+    <t>Figure 9</t>
+  </si>
+  <si>
+    <t>stata/makeTable2.do</t>
+  </si>
+  <si>
+    <t>matlab/makeFigure1.m</t>
+  </si>
+  <si>
+    <t>stata/makeFigures3–7.do</t>
+  </si>
+  <si>
+    <t>matlab/structuralEstimates.m</t>
+  </si>
+  <si>
+    <t>matlab/makeFigure9.m</t>
+  </si>
+  <si>
+    <t>Table A.1</t>
+  </si>
+  <si>
+    <t>stata/makeAppendixTables.do</t>
+  </si>
+  <si>
+    <t>Table A.2</t>
+  </si>
+  <si>
+    <t>Table A.3</t>
+  </si>
+  <si>
+    <t>Table A.4</t>
+  </si>
+  <si>
+    <t>Table A.5</t>
+  </si>
+  <si>
+    <t>Table A.6</t>
+  </si>
+  <si>
+    <t>Table A.7</t>
+  </si>
+  <si>
+    <t>Table A.8</t>
+  </si>
+  <si>
+    <t>Table A.9</t>
+  </si>
+  <si>
+    <t>Figure A.1</t>
+  </si>
+  <si>
+    <t>stata/makeAppendixFigures.do</t>
+  </si>
+  <si>
+    <t>Figure A.2</t>
+  </si>
+  <si>
+    <t>Figure A.3</t>
+  </si>
+  <si>
+    <t>Figure A.4</t>
+  </si>
+  <si>
+    <t>Figure A.5</t>
+  </si>
+  <si>
+    <t>Table C.1</t>
+  </si>
+  <si>
+    <t>Figure C.1</t>
+  </si>
+  <si>
+    <t>Figure D.1</t>
+  </si>
+  <si>
+    <t>Table D.1</t>
+  </si>
+  <si>
+    <t>Table D.2</t>
+  </si>
+  <si>
+    <t>Figure E.1</t>
+  </si>
+  <si>
+    <t>matlab/makeFigureE1.m</t>
+  </si>
+  <si>
+    <t>Figure F.1</t>
+  </si>
+  <si>
+    <t>Figure F.2</t>
+  </si>
+  <si>
+    <t>Figure F.3</t>
+  </si>
+  <si>
+    <t>Table F.1</t>
+  </si>
+  <si>
+    <t>Figure G.1</t>
+  </si>
+  <si>
+    <t>Figure G.2</t>
+  </si>
+  <si>
+    <t>Figure G.3</t>
+  </si>
+  <si>
+    <t>Figure G.4</t>
+  </si>
+  <si>
+    <t>Figure G.5</t>
+  </si>
+  <si>
+    <t>Figure G.6</t>
+  </si>
+  <si>
+    <t>Table G.1</t>
+  </si>
+  <si>
+    <t>R/makeFigureD1.R</t>
+  </si>
+  <si>
+    <t>R/makeTableD1.R</t>
+  </si>
+  <si>
+    <t>R/makeTableD2.R</t>
+  </si>
+  <si>
+    <t>Made by Authors</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Figure 2</t>
+  </si>
+  <si>
+    <t>Table 3</t>
+  </si>
+  <si>
+    <t>In-text claim</t>
+  </si>
+  <si>
+    <t>p. 11: 48 (34%) of 143 CR experiments use KT parameters</t>
+  </si>
+  <si>
+    <t>statsInText.do</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>p. 11: 34 (42%) of 81 CC experiments use Allais parameters</t>
+  </si>
+  <si>
+    <t>p. 19: Average bonus payment $15.76</t>
+  </si>
+  <si>
+    <t>p. 25 (fn 33): ~10% of observations at price list boundaries</t>
+  </si>
+  <si>
+    <t>p. 26 (fn 38): 26% of response patterns are intransitive</t>
+  </si>
+  <si>
+    <t>p. 26 (fn 38): 1.9% average per intransitive pattern</t>
+  </si>
+  <si>
+    <t>p. 26 (fn 38): Only 2 intransitive patterns exceed 3%</t>
+  </si>
+  <si>
+    <t>p. 27: 73% of simulated preferences in 4 strict patterns</t>
+  </si>
+  <si>
+    <t>p. 27: 44% of raw responses in 4 strict patterns</t>
+  </si>
+  <si>
+    <t>p. 27: 8% of simulated preferences in 3 weak patterns</t>
+  </si>
+  <si>
+    <t>p. 27: 11% of raw responses in 3 weak patterns</t>
+  </si>
+  <si>
+    <t>p. 27: 81% of simulated preferences in 7 marked patterns</t>
+  </si>
+  <si>
+    <t>p. 27: 55% of raw responses in 7 marked patterns</t>
+  </si>
+  <si>
+    <t>p. 32: 19% of simulated preferences in other 6 patterns</t>
+  </si>
+  <si>
+    <t>p. 32: 18% of raw responses in other 6 transitive patterns</t>
+  </si>
+  <si>
+    <t>p. 33: ~13% of observations exhibit risk tolerance</t>
+  </si>
+  <si>
+    <t>p. 33: 55% of risk-tolerant exhibit RCRP</t>
+  </si>
+  <si>
+    <t>p. 33: 87% of observations exhibit risk aversion</t>
+  </si>
+  <si>
+    <t>p. 33: 69% of risk-averse exhibit CRP</t>
+  </si>
+  <si>
+    <t>p. 33: Fisher p &lt; 0.001 (Risk Aversion x CRP)</t>
+  </si>
+  <si>
+    <t>p. 33: 48% of risk-tolerant exhibit P1</t>
+  </si>
+  <si>
+    <t>p. 33: 21% of risk-averse exhibit P1</t>
+  </si>
+  <si>
+    <t>p. 33: Fisher p &lt; 0.001 (Risk Aversion x P1)</t>
+  </si>
+  <si>
+    <t>p. 33: 69% of risk-averse exhibit P2/P3/P4</t>
+  </si>
+  <si>
+    <t>p. 33: 45% of risk-tolerant exhibit P2/P3/P4</t>
+  </si>
+  <si>
+    <t>p. 33: Fisher p &lt; 0.001 (Risk Aversion x P2/P3/P4)</t>
+  </si>
+  <si>
+    <t>p. 24: 14.6% exhibit modal pattern</t>
+  </si>
+  <si>
+    <t>p. 24: 21.0% of observations exhibit CR+CC</t>
+  </si>
+  <si>
+    <t>p. 24 (fn 31): 28.9% exhibit CR+CC near canonical parameters</t>
+  </si>
+  <si>
+    <t>p. 24 (fn 31): 13.9% exhibit CR-RCC-MX near canonical parameters</t>
+  </si>
+  <si>
+    <t>p. 24 (fn 31): 21.4% exhibit CR-RCC-MX at small p and small r</t>
+  </si>
+  <si>
+    <t>Line Nuumber</t>
   </si>
 </sst>
 </file>
@@ -434,17 +722,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="54.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -472,33 +761,901 @@
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>91</v>
+      </c>
+      <c r="J3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>133</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7">
+        <v>47</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>47</v>
+      </c>
+      <c r="M8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9">
+        <v>47</v>
+      </c>
+      <c r="M9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10">
+        <v>143</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10">
+        <v>91</v>
+      </c>
+      <c r="M10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11">
+        <v>222</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11">
+        <v>104</v>
+      </c>
+      <c r="M11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>313</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12">
+        <v>104</v>
+      </c>
+      <c r="M12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>146</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13">
+        <v>104</v>
+      </c>
+      <c r="M13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14">
+        <v>132</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15">
+        <v>69</v>
+      </c>
+      <c r="J15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15">
+        <v>132</v>
+      </c>
+      <c r="M15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>92</v>
+      </c>
+      <c r="J16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16">
+        <v>132</v>
+      </c>
+      <c r="M16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <v>112</v>
+      </c>
+      <c r="J17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17">
+        <v>132</v>
+      </c>
+      <c r="M17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18">
+        <v>154</v>
+      </c>
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18">
+        <v>132</v>
+      </c>
+      <c r="M18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19">
+        <v>178</v>
+      </c>
+      <c r="J19" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19">
+        <v>132</v>
+      </c>
+      <c r="M19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20">
+        <v>207</v>
+      </c>
+      <c r="J20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20">
+        <v>175</v>
+      </c>
+      <c r="M20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21">
+        <v>290</v>
+      </c>
+      <c r="J21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21">
+        <v>175</v>
+      </c>
+      <c r="M21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22">
+        <v>436</v>
+      </c>
+      <c r="J22" t="s">
+        <v>86</v>
+      </c>
+      <c r="K22" t="s">
+        <v>70</v>
+      </c>
+      <c r="L22">
+        <v>202</v>
+      </c>
+      <c r="M22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
+        <v>87</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23">
+        <v>202</v>
+      </c>
+      <c r="M23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24">
+        <v>70</v>
+      </c>
+      <c r="J24" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24">
+        <v>202</v>
+      </c>
+      <c r="M24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25">
+        <v>119</v>
+      </c>
+      <c r="J25" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25">
+        <v>202</v>
+      </c>
+      <c r="M25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26">
+        <v>171</v>
+      </c>
+      <c r="J26" t="s">
+        <v>90</v>
+      </c>
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26">
+        <v>202</v>
+      </c>
+      <c r="M26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>350</v>
+      </c>
+      <c r="J27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L27">
+        <v>202</v>
+      </c>
+      <c r="M27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28">
+        <v>509</v>
+      </c>
+      <c r="J28" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28">
+        <v>202</v>
+      </c>
+      <c r="M28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>222</v>
+      </c>
+      <c r="J29" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" t="s">
+        <v>70</v>
+      </c>
+      <c r="L29">
+        <v>202</v>
+      </c>
+      <c r="M29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+      <c r="J30" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30">
+        <v>202</v>
+      </c>
+      <c r="M30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31">
+        <v>28</v>
+      </c>
+      <c r="J31" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31">
+        <v>202</v>
+      </c>
+      <c r="M31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32">
+        <v>27</v>
+      </c>
+      <c r="J32" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32">
+        <v>202</v>
+      </c>
+      <c r="M32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="38" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="39" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="40" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="41" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="42" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="43" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="44" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44">
+        <v>543</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
